--- a/UK_CoP_TitleLists/SciPost_Open_scifreeimport.xlsx
+++ b/UK_CoP_TitleLists/SciPost_Open_scifreeimport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://computingservices-my.sharepoint.com/personal/lc2792_bath_ac_uk/Documents/Documents/SciFree/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d4b02a2393526de/Documents/CoP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="8_{10FF733C-9C67-47F4-BD17-677F06BA0138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0D31B20-788A-472B-932C-356D58C08788}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{FF6880F3-4428-4501-852C-52FEC8E4730B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AEF527C-CFD0-4B54-839E-BA878637F790}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{BE44926E-75A4-4EDC-A463-0127E7F3749D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BE44926E-75A4-4EDC-A463-0127E7F3749D}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal List" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="81">
   <si>
     <t>Journal Title</t>
   </si>
@@ -133,36 +133,6 @@
     <t>Change Type (See Terms)</t>
   </si>
   <si>
-    <t>0123-4566</t>
-  </si>
-  <si>
-    <t>0123-4567</t>
-  </si>
-  <si>
-    <t>https://www.scifree.se</t>
-  </si>
-  <si>
-    <t>Hybrid</t>
-  </si>
-  <si>
-    <t>CC-BY</t>
-  </si>
-  <si>
-    <t>Example Publisher Name</t>
-  </si>
-  <si>
-    <t>EXAMPLE Journal title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E.g. Publisher/Imprint, URL, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">E.g. add new publisher name, add new url, </t>
-  </si>
-  <si>
-    <t>History, Visual Arts and Performing Arts</t>
-  </si>
-  <si>
     <t>Not Accepting Submissions</t>
   </si>
   <si>
@@ -266,13 +236,58 @@
   </si>
   <si>
     <t>https://scipost.org/MigPol</t>
+  </si>
+  <si>
+    <t>Journal of Robustness Reports</t>
+  </si>
+  <si>
+    <t>SciPost Astronomy Codebases</t>
+  </si>
+  <si>
+    <t>SciPost Chemistry Codebases</t>
+  </si>
+  <si>
+    <t>SciPost Chemistry Core</t>
+  </si>
+  <si>
+    <t>SciPost Physics Community Reports</t>
+  </si>
+  <si>
+    <t>SciPost Physics Reviews</t>
+  </si>
+  <si>
+    <t>3051-3200</t>
+  </si>
+  <si>
+    <t>3051-3197</t>
+  </si>
+  <si>
+    <t>https://scipost.org/SciPostAstroCodeb</t>
+  </si>
+  <si>
+    <t>https://scipost.org/JRobustRep</t>
+  </si>
+  <si>
+    <t>https://scipost.org/SciPostChemCodeb</t>
+  </si>
+  <si>
+    <t>https://scipost.org/SciPostChemCore</t>
+  </si>
+  <si>
+    <t>https://scipost.org/SciPostPhysCommRep</t>
+  </si>
+  <si>
+    <t>https://scipost.org/SciPostPhysRev</t>
+  </si>
+  <si>
+    <t>New journal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -305,13 +320,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -329,13 +337,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -365,12 +366,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF646464"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -381,22 +376,10 @@
       <family val="2"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <name val="Arial Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF646464"/>
-      <name val="Arial Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF646464"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -407,7 +390,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -527,15 +510,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -553,271 +527,101 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="35">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -830,7 +634,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color rgb="FF000000"/>
+        <color auto="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -842,459 +646,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1605,6 +956,68 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <top style="thin">
           <color theme="9" tint="-0.499984740745262"/>
@@ -1625,6 +1038,66 @@
         <bottom style="thin">
           <color theme="9" tint="-0.499984740745262"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1639,7 +1112,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color auto="1"/>
+        <color rgb="FF000000"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -1651,6 +1124,482 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <border>
@@ -1713,51 +1662,55 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E20557D-7D01-4DDD-A3E5-4BE8969774E1}" name="Table1" displayName="Table1" ref="A1:H14" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33" tableBorderDxfId="31" totalsRowBorderDxfId="30">
-  <autoFilter ref="A1:H14" xr:uid="{4E20557D-7D01-4DDD-A3E5-4BE8969774E1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E20557D-7D01-4DDD-A3E5-4BE8969774E1}" name="Table1" displayName="Table1" ref="A1:H16" totalsRowShown="0" headerRowDxfId="34" dataDxfId="0" headerRowBorderDxfId="33" tableBorderDxfId="32" totalsRowBorderDxfId="31">
+  <autoFilter ref="A1:H16" xr:uid="{4E20557D-7D01-4DDD-A3E5-4BE8969774E1}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{60C9D913-7610-4E89-96C3-79D540E13C81}" name="Journal Title" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{157A6765-6BEB-45C8-B059-14466701E200}" name="Imprint" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{C2D0AE15-8EB6-42FA-9756-6359A70C39F2}" name="Print ISSN" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{C1A14781-2EC2-4655-8B99-34C639B681F7}" name="Electronic ISSN" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{6A1CDB50-05D6-4137-BED6-66AEA762C1D8}" name="Journal URL" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{142F869A-41EF-4110-B212-DCDFE3A91B4D}" name="Publishing Model" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{883DC121-F62A-4717-ABC9-50C24089DAAE}" name="License Options" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{79ADE6AD-15D5-4E9E-ADB0-716C42F18B23}" name="Subject Areas" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{60C9D913-7610-4E89-96C3-79D540E13C81}" name="Journal Title" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{157A6765-6BEB-45C8-B059-14466701E200}" name="Imprint" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{C2D0AE15-8EB6-42FA-9756-6359A70C39F2}" name="Print ISSN" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{C1A14781-2EC2-4655-8B99-34C639B681F7}" name="Electronic ISSN" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{6A1CDB50-05D6-4137-BED6-66AEA762C1D8}" name="Journal URL" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{142F869A-41EF-4110-B212-DCDFE3A91B4D}" name="Publishing Model" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{883DC121-F62A-4717-ABC9-50C24089DAAE}" name="License Options" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{79ADE6AD-15D5-4E9E-ADB0-716C42F18B23}" name="Subject Areas" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{50DE42A8-741C-4C2A-82B7-4C9C79D7B512}" name="Table14" displayName="Table14" ref="A4:J23" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{50DE42A8-741C-4C2A-82B7-4C9C79D7B512}" name="Table14" displayName="Table14" ref="A4:J23" totalsRowShown="0" headerRowDxfId="30" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27" totalsRowBorderDxfId="26">
   <autoFilter ref="A4:J23" xr:uid="{50DE42A8-741C-4C2A-82B7-4C9C79D7B512}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{1B9A1423-FE7E-41D7-B053-6BF091F459D2}" name="Journal Title" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{B625EB42-AF86-4F71-BC2F-65D99997CD50}" name="Imprint" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{559DDF72-C949-47E4-8DA4-297063A6725C}" name="Print ISSN" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{2C5C0518-FAE9-4E34-9C5C-031EDE4262BA}" name="Electronic ISSN" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{D5474278-5905-4A79-9DFE-DE4AB9980E12}" name="Journal URL" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{3D861C40-F9D7-4168-ACD1-389CE9995730}" name="Publishing Model" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{156C7878-43A4-40BA-84D1-0BD24E590EEE}" name="License Options" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{4C684C0B-6FA6-4E1F-BC47-B228FA209770}" name="Subject Areas" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{96CDE76D-4B76-48A4-98FB-70E2CCC4CFC8}" name="Change Type (See Terms)" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{43B192BA-2299-4882-A245-9C663CF7CF9B}" name="Change Note" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{1B9A1423-FE7E-41D7-B053-6BF091F459D2}" name="Journal Title" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{B625EB42-AF86-4F71-BC2F-65D99997CD50}" name="Imprint" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{559DDF72-C949-47E4-8DA4-297063A6725C}" name="Print ISSN" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{2C5C0518-FAE9-4E34-9C5C-031EDE4262BA}" name="Electronic ISSN" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{D5474278-5905-4A79-9DFE-DE4AB9980E12}" name="Journal URL" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{3D861C40-F9D7-4168-ACD1-389CE9995730}" name="Publishing Model" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{156C7878-43A4-40BA-84D1-0BD24E590EEE}" name="License Options" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{4C684C0B-6FA6-4E1F-BC47-B228FA209770}" name="Subject Areas" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{96CDE76D-4B76-48A4-98FB-70E2CCC4CFC8}" name="Change Type (See Terms)" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{43B192BA-2299-4882-A245-9C663CF7CF9B}" name="Change Note" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{98A0D124-AED4-4DBE-8354-EE3315983F60}" name="Table25" displayName="Table25" ref="A1:B11" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5" tableBorderDxfId="3" totalsRowBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{98A0D124-AED4-4DBE-8354-EE3315983F60}" name="Table25" displayName="Table25" ref="A1:B11" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
   <autoFilter ref="A1:B11" xr:uid="{98A0D124-AED4-4DBE-8354-EE3315983F60}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B11">
     <sortCondition ref="A1:A11"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E088FFDE-8F3A-4B84-9B24-F82FF70FAEA5}" name="Term" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{3BB7484B-180C-438A-8248-E8FEA43CCABB}" name="Description" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{E088FFDE-8F3A-4B84-9B24-F82FF70FAEA5}" name="Term" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{3BB7484B-180C-438A-8248-E8FEA43CCABB}" name="Description" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2080,10 +2033,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D4A9487-D5B7-4CE1-99CD-1488FAF55674}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.54296875" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.1796875" style="12" customWidth="1"/>
     <col min="3" max="3" width="11.36328125" style="12" customWidth="1"/>
     <col min="4" max="4" width="16" style="12" customWidth="1"/>
@@ -2120,272 +2073,356 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="39" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="40" t="s">
+    <row r="2" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="34"/>
+      <c r="D2" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="34"/>
+      <c r="D3" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="34"/>
+      <c r="D4" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="27"/>
+    </row>
+    <row r="5" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="D8" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B10" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" spans="1:11" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42" t="s">
+      <c r="B12" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="34" t="s">
+      <c r="H12" s="36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G3" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="H3" s="48" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="47" t="s">
+      <c r="B13" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="G13" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="H4" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="K4" s="45"/>
-    </row>
-    <row r="5" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46" t="s">
+      <c r="B14" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="H5" s="48" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="50" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="46"/>
-      <c r="D6" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="34" t="s">
+      <c r="B15" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="F6" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="H6" s="48" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="50" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="F7" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="H7" s="48" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="50" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="46"/>
-      <c r="D8" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" s="48" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="49" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="38" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="50" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" s="48" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="15"/>
-    </row>
-    <row r="12" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="15"/>
-    </row>
-    <row r="13" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="15"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="16"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
+      <c r="B16" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" s="36" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2422,322 +2459,385 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
     </row>
     <row r="4" spans="1:10" ht="31" x14ac:dyDescent="0.35">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="31" t="s">
+      <c r="H4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="I4" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="24" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:10" ht="31" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="14"/>
+      <c r="I5" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" s="16"/>
+    </row>
+    <row r="6" spans="1:10" ht="31" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:10" ht="31" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="J7" s="19"/>
+    </row>
+    <row r="8" spans="1:10" ht="31" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="19"/>
+    </row>
+    <row r="9" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="27"/>
-    </row>
-    <row r="7" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="27"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="27"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="27"/>
-    </row>
-    <row r="10" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="27"/>
+      <c r="I9" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="19"/>
+    </row>
+    <row r="10" spans="1:10" ht="31" x14ac:dyDescent="0.35">
+      <c r="A10" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" s="19"/>
     </row>
     <row r="11" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="27"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="19"/>
     </row>
     <row r="12" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="27"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="19"/>
     </row>
     <row r="13" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="27"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="19"/>
     </row>
     <row r="14" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="27"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="19"/>
     </row>
     <row r="15" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="27"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="19"/>
     </row>
     <row r="16" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="25"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="27"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="19"/>
     </row>
     <row r="17" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="27"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="19"/>
     </row>
     <row r="18" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="27"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="19"/>
     </row>
     <row r="19" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="27"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="19"/>
     </row>
     <row r="20" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="25"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="27"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="19"/>
     </row>
     <row r="21" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="25"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="27"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="19"/>
     </row>
     <row r="22" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="27"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="19"/>
     </row>
     <row r="23" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="30"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J2"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="E5" r:id="rId1" xr:uid="{A941C51A-735A-424E-9F09-945F539595B9}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2801,7 +2901,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>21</v>
